--- a/output/pdf_financials_xlsx/KCLI.xlsx
+++ b/output/pdf_financials_xlsx/KCLI.xlsx
@@ -2194,16 +2194,16 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>0.314545</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>0.352982</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>0.362064</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>0.367692</v>
       </c>
     </row>
     <row r="92">
@@ -2213,16 +2213,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.450191</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.676225</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.806929</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.348001</v>
       </c>
     </row>
     <row r="93">
@@ -3496,7 +3496,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -3528,7 +3532,11 @@
           <t>Warrant reserve 7</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3560,7 +3568,11 @@
           <t>Foreign translation reserve 7</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3888,7 +3900,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>1.531176</v>
       </c>
@@ -3922,7 +3938,11 @@
           <t>Warrant reserve 8</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>0.919015</v>
       </c>
@@ -3956,7 +3976,11 @@
           <t>Foreign translation reserve</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>0.314545</v>
       </c>

--- a/output/pdf_financials_xlsx/KCLI.xlsx
+++ b/output/pdf_financials_xlsx/KCLI.xlsx
@@ -642,13 +642,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000182</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.013963</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.020035</v>
       </c>
     </row>
     <row r="13">
@@ -945,13 +945,13 @@
         <v>-0.360485</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.406042</v>
+        <v>-1.406224</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.599012</v>
+        <v>-0.612975</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.605044</v>
+        <v>-1.625079</v>
       </c>
     </row>
     <row r="28">
@@ -983,13 +983,13 @@
         <v>-0.360485</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.406042</v>
+        <v>-1.406224</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.599012</v>
+        <v>-0.612975</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.605044</v>
+        <v>-1.625079</v>
       </c>
     </row>
     <row r="30">
@@ -1079,16 +1079,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.091489</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.234997</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.003348</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.400564</v>
       </c>
     </row>
     <row r="35">
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.091489</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.234997</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.003348</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.400564</v>
       </c>
     </row>
     <row r="37">
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.122745</v>
+        <v>0.031256</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.497197</v>
+        <v>0.2622</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.03102</v>
+        <v>0.027672</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.467798</v>
+        <v>0.067234</v>
       </c>
     </row>
     <row r="49">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4288,7 +4288,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -6452,7 +6456,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6764,7 +6768,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">

--- a/output/pdf_financials_xlsx/KCLI.xlsx
+++ b/output/pdf_financials_xlsx/KCLI.xlsx
@@ -1657,16 +1657,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.032305</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.057364</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.222991</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.14362</v>
       </c>
     </row>
     <row r="65">
@@ -1714,16 +1714,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.035574</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.07575</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.104364</v>
       </c>
     </row>
     <row r="68">
